--- a/templates/weekly-plan-template.xlsx
+++ b/templates/weekly-plan-template.xlsx
@@ -224,7 +224,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">T. Hughes</t>
+          <t xml:space="preserve">K. Ahmed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -234,12 +234,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -249,19 +249,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">S. Malik</t>
+          <t xml:space="preserve">T. Hughes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -286,19 +286,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">B. Carter</t>
+          <t xml:space="preserve">S. Malik</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -313,12 +313,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -328,14 +328,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">L. Osei</t>
+          <t xml:space="preserve">B. Carter</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -345,17 +345,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -365,14 +365,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar</t>
+          <t xml:space="preserve">L. Osei</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -382,12 +382,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -397,19 +397,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hannah</t>
+          <t xml:space="preserve">Omar</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -419,34 +419,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel</t>
+          <t xml:space="preserve">Hannah</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -456,34 +456,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH LAB</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHH - DAY UNIT</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHH - DAY UNIT</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHH - DAY UNIT</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHH - DAY UNIT</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zara</t>
+          <t xml:space="preserve">Daniel</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -493,34 +493,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH MDCU</t>
+          <t xml:space="preserve">GUH LAB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">NHH - DAY UNIT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">NHH - DAY UNIT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">NHH - DAY UNIT</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">NHH - DAY UNIT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meera</t>
+          <t xml:space="preserve">Zara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -530,27 +530,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH LAB</t>
+          <t xml:space="preserve">RGH MDCU</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH LAB</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -572,57 +572,94 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">GUH LAB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t xml:space="preserve">OFF</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GUH</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GUH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Meera</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH LAB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OFF</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yusuf</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">RGH MDCU</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RGH</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RGH</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RGH</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RGH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">OFF</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">RGH</t>
         </is>
@@ -762,10 +799,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">INDUCTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t xml:space="preserve">SpR TRAINING DAY</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">SpR training day</t>
         </is>

--- a/templates/weekly-plan-template.xlsx
+++ b/templates/weekly-plan-template.xlsx
@@ -409,7 +409,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omar</t>
+          <t xml:space="preserve">New F1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -446,7 +446,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hannah</t>
+          <t xml:space="preserve">New F2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -456,34 +456,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">NHH</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">NHH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">NHH</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH - DAY UNIT</t>
+          <t xml:space="preserve">NHH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel</t>
+          <t xml:space="preserve">Omar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -493,34 +493,34 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH LAB</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHH - DAY UNIT</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHH - DAY UNIT</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHH - DAY UNIT</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHH - DAY UNIT</t>
+          <t xml:space="preserve">GUH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zara</t>
+          <t xml:space="preserve">Hannah</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -530,34 +530,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH MDCU</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RGH</t>
+          <t xml:space="preserve">RGH - DAY UNIT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meera</t>
+          <t xml:space="preserve">Daniel</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -572,94 +572,168 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH LAB</t>
+          <t xml:space="preserve">NHH - DAY UNIT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">NHH - DAY UNIT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">NHH - DAY UNIT</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">NHH - DAY UNIT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meera</t>
+          <t xml:space="preserve">Zara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH LAB</t>
+          <t xml:space="preserve">RGH MDCU</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFF</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUH</t>
+          <t xml:space="preserve">RGH</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Meera</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH LAB</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH LAB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meera</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH LAB</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OFF</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yusuf</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">RGH MDCU</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RGH</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RGH</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RGH</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RGH</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">OFF</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">RGH</t>
         </is>
